--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,114 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Minsk</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>226</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>155</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>noche</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>155</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>noche</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clima.xlsx
+++ b/clima.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="140" windowWidth="14890" windowHeight="14980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clima" sheetId="1" state="visible" r:id="rId1"/>

--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1107,6 +1107,42 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Santa fe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sureste</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1143,6 +1143,42 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>651</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1071,114 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>651</v>
-      </c>
-      <c r="E19" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>dia</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Noreste</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nublado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Santa fe</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>23</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Día</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Sureste</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Nublado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>651</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Día</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Noreste</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Muy nublado</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
